--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104622_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104622_W19.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5776</v>
+        <v>6.0194</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4916</v>
+        <v>5.8071</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2123</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8693</v>
+        <v>5.86</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0634</v>
+        <v>1.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8059</v>
+        <v>4.7946</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9323</v>
+        <v>5.9002</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0492</v>
+        <v>1.0375</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8831</v>
+        <v>4.8627</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.063</v>
+        <v>-0.0402</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0959</v>
+        <v>0.5448</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1724</v>
+        <v>0.1833</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2683</v>
+        <v>0.3616</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0744</v>
+        <v>4.0162</v>
       </c>
       <c r="E3" t="n">
-        <v>2.015</v>
+        <v>1.8708</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0594</v>
+        <v>2.1454</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3052</v>
+        <v>4.3681</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9236</v>
+        <v>2.4793</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.8888</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4192</v>
+        <v>4.8965</v>
       </c>
       <c r="K3" t="n">
-        <v>2.019</v>
+        <v>3.5713</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5998</v>
+        <v>1.3252</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.114</v>
+        <v>-0.5284</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0954</v>
+        <v>-1.092</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>0.5636</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9545</v>
+        <v>-0.2137</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5958</v>
+        <v>-0.156</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3587</v>
+        <v>-0.0578</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1875</v>
+        <v>3.7726</v>
       </c>
       <c r="E4" t="n">
-        <v>1.26</v>
+        <v>1.8799</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9275</v>
+        <v>1.8927</v>
       </c>
       <c r="G4" t="n">
-        <v>4.382</v>
+        <v>1.301</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4922</v>
+        <v>1.9161</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8899</v>
+        <v>-0.6151</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9328</v>
+        <v>1.3993</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5948</v>
+        <v>2.0027</v>
       </c>
       <c r="L4" t="n">
-        <v>1.338</v>
+        <v>-0.6035</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5507</v>
+        <v>-0.0982</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1026</v>
+        <v>-0.0866</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0604</v>
+        <v>0.6505</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8166</v>
+        <v>0.4806</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2438</v>
+        <v>0.1699</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0377</v>
+        <v>3.187</v>
       </c>
       <c r="E5" t="n">
-        <v>1.666</v>
+        <v>1.4771</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3717</v>
+        <v>1.7099</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3904</v>
+        <v>0.3903</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7503</v>
+        <v>0.7524</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3599</v>
+        <v>-0.3621</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5521</v>
+        <v>0.5319</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1617</v>
+        <v>-0.1416</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2601</v>
+        <v>-0.1138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0212</v>
+        <v>-0.1443</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2813</v>
+        <v>0.0305</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>J. COBBS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8395</v>
+        <v>1.3742</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001</v>
+        <v>3.009</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8405</v>
+        <v>-1.6348</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7613</v>
+        <v>1.8434</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6306</v>
+        <v>-0.3266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1307</v>
+        <v>2.17</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3717</v>
+        <v>2.1706</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2224</v>
+        <v>-0.3834</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1493</v>
+        <v>2.554</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3896</v>
+        <v>-0.3271</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4082</v>
+        <v>0.0568</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0186</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7587</v>
+        <v>0.165</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7349</v>
+        <v>-0.0234</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0238</v>
+        <v>0.1884</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7071</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9539</v>
+        <v>1.1362</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2915</v>
+        <v>-0.2582</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3376</v>
+        <v>1.3944</v>
       </c>
       <c r="G7" t="n">
-        <v>1.141</v>
+        <v>1.7632</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0372</v>
+        <v>1.6259</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1782</v>
+        <v>0.1373</v>
       </c>
       <c r="J7" t="n">
-        <v>1.015</v>
+        <v>1.3588</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2313</v>
+        <v>1.2098</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7837</v>
+        <v>0.1489</v>
       </c>
       <c r="M7" t="n">
-        <v>0.126</v>
+        <v>0.4044</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2685</v>
+        <v>0.416</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3946</v>
+        <v>-0.0116</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4745</v>
+        <v>1.0559</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4748</v>
+        <v>0.5016</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0003</v>
+        <v>0.5543</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2495</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0285</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.278</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. COBBS</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8431</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8177</v>
+        <v>2.1347</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9746</v>
+        <v>-1.2713</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8662</v>
+        <v>1.1312</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3114</v>
+        <v>-0.0564</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1777</v>
+        <v>1.1876</v>
       </c>
       <c r="J8" t="n">
-        <v>2.212</v>
+        <v>0.9846</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3574</v>
+        <v>0.2026</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5694</v>
+        <v>0.782</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3458</v>
+        <v>0.1467</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>-0.259</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3918</v>
+        <v>0.4057</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3841</v>
+        <v>0.3891</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2601</v>
+        <v>0.3597</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.124</v>
+        <v>0.0294</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-2.2504</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.018</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1939</v>
+        <v>-0.6954</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2808</v>
+        <v>-2.4608</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0869</v>
+        <v>1.7654</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.294</v>
+        <v>-0.2832</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2887</v>
+        <v>-0.2818</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0053</v>
+        <v>-0.0013</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0337</v>
+        <v>-0.0402</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2603</v>
+        <v>-0.243</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0074</v>
+        <v>0.4983</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0212</v>
+        <v>-0.1443</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9863</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8595</v>
+        <v>-1.4787</v>
       </c>
       <c r="E10" t="n">
-        <v>0.464</v>
+        <v>-0.0158</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3235</v>
+        <v>-1.4629</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0965</v>
+        <v>-1.0894</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0809</v>
+        <v>-0.075</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0156</v>
+        <v>-1.0144</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0039</v>
+        <v>-0.0015</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1003</v>
+        <v>-1.0879</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4884</v>
+        <v>-0.1405</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5263</v>
+        <v>0.0556</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0378</v>
+        <v>-0.1961</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.831</v>
+        <v>-2.0401</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2494</v>
+        <v>-2.5056</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4184</v>
+        <v>0.4655</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9793</v>
+        <v>-1.9806</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6969</v>
+        <v>0.6979</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6762</v>
+        <v>-2.6784</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3667</v>
+        <v>-1.3809</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6126</v>
+        <v>-0.5997</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2144</v>
+        <v>0.0104</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3176</v>
+        <v>0.0834</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1031</v>
+        <v>-0.073</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7676</v>
+        <v>-2.4522</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.829</v>
+        <v>-2.6522</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0614</v>
+        <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1142</v>
+        <v>-3.1141</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7951</v>
+        <v>-0.7901</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.319</v>
+        <v>-2.324</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2725</v>
+        <v>-2.2827</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8417</v>
+        <v>-0.8314</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8817</v>
+        <v>-0.8763</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5607</v>
+        <v>-0.2486</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5565</v>
+        <v>-0.3695</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8427</v>
+        <v>-3.3432</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5113</v>
+        <v>-2.103</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3314</v>
+        <v>-1.2401</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5185</v>
+        <v>-1.5057</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7691</v>
+        <v>-1.7638</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2506</v>
+        <v>0.258</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5705</v>
+        <v>-0.5745</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L13" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.948</v>
+        <v>-0.9312</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5511</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2141</v>
+        <v>0.2766</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.019</v>
+        <v>10.3594</v>
       </c>
       <c r="E14" t="n">
-        <v>6.134300000000001</v>
+        <v>6.183</v>
       </c>
       <c r="F14" t="n">
-        <v>3.884699999999999</v>
+        <v>4.1765</v>
       </c>
       <c r="G14" t="n">
-        <v>8.712899999999998</v>
+        <v>8.684200000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2746</v>
+        <v>5.2433</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4386</v>
+        <v>3.441</v>
       </c>
       <c r="J14" t="n">
-        <v>13.1956</v>
+        <v>12.9621</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5575</v>
+        <v>10.419</v>
       </c>
       <c r="L14" t="n">
-        <v>2.638199999999999</v>
+        <v>2.542999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.4825</v>
+        <v>-4.2776</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.282999999999999</v>
+        <v>-5.175599999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8005</v>
+        <v>0.8980000000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4026</v>
+        <v>3.4146</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6098</v>
+        <v>-13.6578</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0126</v>
+        <v>17.0726</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1774</v>
+        <v>2.5323</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1209999999999999</v>
+        <v>0.4850000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0567</v>
+        <v>2.0473</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.2742</v>
+        <v>-4.2716</v>
       </c>
       <c r="W14" t="n">
-        <v>6.427700000000001</v>
+        <v>6.3941</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.7018</v>
+        <v>-10.6654</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.932</v>
+        <v>3.5773</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1853</v>
+        <v>3.9731</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2533</v>
+        <v>-0.3958</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8166</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3578</v>
+        <v>-1.3585</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1698</v>
+        <v>2.1751</v>
       </c>
       <c r="J15" t="n">
-        <v>1.863</v>
+        <v>1.8329</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1865</v>
+        <v>0.1649</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0511</v>
+        <v>-1.0163</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5443</v>
+        <v>-1.5233</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1068</v>
+        <v>-0.467</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1825</v>
+        <v>-0.3558</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9243</v>
+        <v>-0.1111</v>
       </c>
       <c r="V15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9044</v>
+        <v>0.7121</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5513</v>
+        <v>1.1711</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6469</v>
+        <v>-0.459</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4843</v>
+        <v>0.4989</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0809</v>
+        <v>-0.075</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5652</v>
+        <v>0.5739</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3068</v>
+        <v>1.3011</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8225</v>
+        <v>-0.8022</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5051</v>
+        <v>0.309</v>
       </c>
       <c r="T16" t="n">
-        <v>0.369</v>
+        <v>0.0161</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1361</v>
+        <v>0.2929</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W16" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2526</v>
+        <v>-0.1946</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7212</v>
+        <v>-1.0499</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4686</v>
+        <v>0.8554</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4586</v>
+        <v>-0.2366</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6479</v>
+        <v>0.5684</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1893</v>
+        <v>-0.805</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3715</v>
+        <v>1.1941</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5208</v>
+        <v>1.7614</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>-0.5673</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0871</v>
+        <v>-1.4307</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1272</v>
+        <v>-1.1931</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04</v>
+        <v>-0.2377</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4594</v>
+        <v>-0.7711</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8771</v>
+        <v>-0.7809</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4177</v>
+        <v>0.0097</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="W17" t="n">
+        <v>2.1789</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.1607</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8021</v>
+        <v>-0.3848</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4582</v>
+        <v>-1.3326</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6562</v>
+        <v>0.9478</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2291</v>
+        <v>-2.9155</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5627</v>
+        <v>-3.1017</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.1862</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2378</v>
+        <v>-1.7831</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7765</v>
+        <v>-2.2967</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5387</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.467</v>
+        <v>-1.1325</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2139</v>
+        <v>-0.805</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2531</v>
+        <v>-0.3275</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3973</v>
+        <v>-0.1522</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2521</v>
+        <v>-0.4114</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1452</v>
+        <v>0.2592</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1262</v>
+        <v>-0.6374</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0804</v>
+        <v>-1.3162</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0457</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8263</v>
+        <v>-1.4492</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1573</v>
+        <v>-1.6431</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9835</v>
+        <v>0.1939</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9032</v>
+        <v>-1.3786</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8658</v>
+        <v>-1.5276</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.1489</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7294</v>
+        <v>-0.0706</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7086</v>
+        <v>-0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0209</v>
+        <v>0.0449</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.007</v>
+        <v>0.0591</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>0.29</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5495</v>
+        <v>-0.2309</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1466</v>
+        <v>-1.2261</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6592</v>
+        <v>0.0242</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5125999999999999</v>
+        <v>-1.2504</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9128</v>
+        <v>-0.8205</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0994</v>
+        <v>0.1579</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1866</v>
+        <v>-0.9785</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7599</v>
+        <v>0.8991</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2796</v>
+        <v>0.8618</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.153</v>
+        <v>-1.7196</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8198</v>
+        <v>-0.7039</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3331</v>
+        <v>-1.0157</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9143</v>
+        <v>-0.1081</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7652</v>
+        <v>-0.4392</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1491</v>
+        <v>0.3311</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.511</v>
+        <v>-2.1575</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2428</v>
+        <v>-0.3792</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7538</v>
+        <v>-1.7782</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.274</v>
+        <v>-1.2793</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6794</v>
+        <v>-1.6897</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2865</v>
+        <v>-0.3207</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0434</v>
+        <v>2.0339</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3299</v>
+        <v>-2.3547</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9875</v>
+        <v>-0.9585</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8142</v>
+        <v>0.1626</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5293</v>
+        <v>-0.0585</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2849</v>
+        <v>0.2211</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2163</v>
+        <v>-2.4891</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3292</v>
+        <v>-1.5422</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5456</v>
+        <v>-0.9469</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0432</v>
+        <v>-0.8305</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0218</v>
+        <v>1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0214</v>
+        <v>-2.1405</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0633</v>
+        <v>1.1469</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6825</v>
+        <v>1.8993</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7458</v>
+        <v>-0.7524</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1065</v>
+        <v>-1.9774</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3393</v>
+        <v>-0.5893</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7672</v>
+        <v>-1.3881</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8949</v>
+        <v>0.2519</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6684</v>
+        <v>-0.0258</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2265</v>
+        <v>0.2777</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3668</v>
+        <v>-2.7698</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3972</v>
+        <v>-0.2927</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9697</v>
+        <v>-2.4772</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.827</v>
+        <v>-2.0416</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3161</v>
+        <v>-2.0083</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1431</v>
+        <v>-0.0333</v>
       </c>
       <c r="J23" t="n">
-        <v>1.166</v>
+        <v>1.0409</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9151</v>
+        <v>-0.6862</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>1.7271</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.993</v>
+        <v>-3.0825</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.599</v>
+        <v>-1.3221</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.394</v>
+        <v>-1.7604</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3675</v>
+        <v>0.3401</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0907</v>
+        <v>0.0809</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2767</v>
+        <v>0.2592</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4338</v>
+        <v>-2.8618</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.877</v>
+        <v>-3.4321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4433</v>
+        <v>0.5703</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4382</v>
+        <v>-0.4266</v>
       </c>
       <c r="H24" t="n">
-        <v>0.492</v>
+        <v>0.4966</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9302</v>
+        <v>-0.9233</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3602</v>
+        <v>0.3451</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7836</v>
+        <v>1.7754</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7984</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7933</v>
+        <v>-0.2287</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0414</v>
+        <v>0.1339</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.019</v>
+        <v>-8.431699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.884600000000001</v>
+        <v>-4.176500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.134300000000001</v>
+        <v>-4.255100000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.712899999999999</v>
+        <v>-8.6843</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.274299999999999</v>
+        <v>-5.243300000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4385</v>
+        <v>-3.441199999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>4.482399999999999</v>
+        <v>4.2777</v>
       </c>
       <c r="K25" t="n">
-        <v>5.282900000000001</v>
+        <v>5.1755</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8003999999999997</v>
+        <v>-0.8981999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.1955</v>
+        <v>-12.962</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.5576</v>
+        <v>-10.4188</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.6382</v>
+        <v>-2.543099999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4026</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R25" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1776</v>
+        <v>-0.6044000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.0565</v>
+        <v>-2.0473</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1212</v>
+        <v>1.4428</v>
       </c>
       <c r="V25" t="n">
-        <v>4.2742</v>
+        <v>4.271599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>10.7019</v>
+        <v>10.6655</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.4276</v>
+        <v>-6.394</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104622_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104622_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.6654</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104622_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.394</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
